--- a/05_생산실적/조립비정산/05월/오류리스트_04월_WAMAS01등록요청.xlsx
+++ b/05_생산실적/조립비정산/05월/오류리스트_04월_WAMAS01등록요청.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J387"/>
+  <dimension ref="A1:J383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" style="15" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="1" ht="17.25" customHeight="1" s="15">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>4월 RETRACTOR WAMAS01 기준정보 등록 요청 리스트</t>
+          <t>4월 RETRACTOR WAMAS01 라인코드 등록 요청 리스트</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2425,12 +2425,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2569,12 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3385,12 +3385,12 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3721,12 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4201,12 +4201,12 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4297,12 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J79" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4393,12 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4777,12 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4873,12 +4873,12 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5209,12 +5209,12 @@
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5257,12 +5257,12 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5689,12 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5833,12 +5833,12 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5977,12 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6025,12 +6025,12 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6361,12 +6361,12 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6697,12 +6697,12 @@
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6745,12 @@
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6889,12 +6889,12 @@
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6937,12 +6937,12 @@
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7177,12 +7177,12 @@
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7417,12 +7417,12 @@
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J144" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7513,12 +7513,12 @@
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7657,12 +7657,12 @@
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J148" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J150" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7801,12 +7801,12 @@
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J152" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7945,12 +7945,12 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J154" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7993,12 @@
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J158" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J160" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8281,12 +8281,12 @@
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8329,12 +8329,12 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J162" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8425,12 +8425,12 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J164" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8473,12 +8473,12 @@
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J166" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8569,12 +8569,12 @@
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J168" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J170" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8761,12 @@
       </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J172" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J174" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9001,12 +9001,12 @@
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J178" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J180" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9289,12 +9289,12 @@
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J182" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9337,12 +9337,12 @@
       </c>
       <c r="I183" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J184" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9433,12 +9433,12 @@
       </c>
       <c r="I185" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9481,12 +9481,12 @@
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J186" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J187" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9577,12 +9577,12 @@
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J188" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9625,12 @@
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J190" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9721,12 +9721,12 @@
       </c>
       <c r="I191" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J192" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9817,12 +9817,12 @@
       </c>
       <c r="I193" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J194" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J196" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I197" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J197" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J198" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10105,12 +10105,12 @@
       </c>
       <c r="I199" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J200" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10201,12 +10201,12 @@
       </c>
       <c r="I201" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J201" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10249,12 +10249,12 @@
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J202" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J203" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10345,12 +10345,12 @@
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J204" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="I205" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10441,12 +10441,12 @@
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J206" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10489,12 +10489,12 @@
       </c>
       <c r="I207" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J207" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10537,12 @@
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J208" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="I209" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J209" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10633,12 +10633,12 @@
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       </c>
       <c r="I211" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J211" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J212" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10777,12 +10777,12 @@
       </c>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J213" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10825,12 +10825,12 @@
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J214" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="I215" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10921,12 +10921,12 @@
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J216" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -10969,12 +10969,12 @@
       </c>
       <c r="I217" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11017,12 @@
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J218" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11065,12 +11065,12 @@
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J219" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11113,12 +11113,12 @@
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J220" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11161,12 +11161,12 @@
       </c>
       <c r="I221" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11209,12 +11209,12 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11257,12 +11257,12 @@
       </c>
       <c r="I223" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J224" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11353,12 +11353,12 @@
       </c>
       <c r="I225" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J225" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J226" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11449,12 @@
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J227" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11497,12 +11497,12 @@
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J228" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="I229" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11593,12 +11593,12 @@
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J230" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11641,12 @@
       </c>
       <c r="I231" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11689,12 +11689,12 @@
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J232" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="I233" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11833,12 +11833,12 @@
       </c>
       <c r="I235" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11881,12 +11881,12 @@
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J236" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11929,12 +11929,12 @@
       </c>
       <c r="I237" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J237" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -11977,12 +11977,12 @@
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J238" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12025,12 +12025,12 @@
       </c>
       <c r="I239" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J239" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12073,12 +12073,12 @@
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J240" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12121,12 +12121,12 @@
       </c>
       <c r="I241" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J241" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J242" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12217,12 +12217,12 @@
       </c>
       <c r="I243" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J243" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12265,12 @@
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J244" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="I245" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12361,12 +12361,12 @@
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J246" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12409,12 +12409,12 @@
       </c>
       <c r="I247" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12457,12 @@
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J248" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12505,12 +12505,12 @@
       </c>
       <c r="I249" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J249" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J250" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12601,12 +12601,12 @@
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J251" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12649,12 +12649,12 @@
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="I253" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12745,12 +12745,12 @@
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J254" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="I255" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J256" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12889,12 +12889,12 @@
       </c>
       <c r="I257" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J258" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -12985,12 +12985,12 @@
       </c>
       <c r="I259" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13033,12 +13033,12 @@
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J260" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13081,12 +13081,12 @@
       </c>
       <c r="I261" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13129,12 +13129,12 @@
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J262" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="I263" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J264" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13273,12 +13273,12 @@
       </c>
       <c r="I265" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J266" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13369,12 +13369,12 @@
       </c>
       <c r="I267" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13417,12 +13417,12 @@
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J268" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="I269" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J269" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J270" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13561,12 +13561,12 @@
       </c>
       <c r="I271" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13609,12 +13609,12 @@
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J272" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13657,12 +13657,12 @@
       </c>
       <c r="I273" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J274" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="I275" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J275" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J276" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13849,12 +13849,12 @@
       </c>
       <c r="I277" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J278" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13945,12 +13945,12 @@
       </c>
       <c r="I279" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -13993,12 +13993,12 @@
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14041,12 @@
       </c>
       <c r="I281" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14089,12 +14089,12 @@
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="I283" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14185,12 +14185,12 @@
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14233,12 +14233,12 @@
       </c>
       <c r="I285" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14281,12 +14281,12 @@
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="I287" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14377,12 +14377,12 @@
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J288" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14425,12 +14425,12 @@
       </c>
       <c r="I289" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14473,12 @@
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14521,12 +14521,12 @@
       </c>
       <c r="I291" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14569,12 +14569,12 @@
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14617,12 +14617,12 @@
       </c>
       <c r="I293" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J294" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14713,12 +14713,12 @@
       </c>
       <c r="I295" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14761,12 +14761,12 @@
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="I297" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14857,12 +14857,12 @@
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J298" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14905,12 +14905,12 @@
       </c>
       <c r="I299" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15001,12 +15001,12 @@
       </c>
       <c r="I301" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15049,12 +15049,12 @@
       </c>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15097,12 +15097,12 @@
       </c>
       <c r="I303" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15145,12 +15145,12 @@
       </c>
       <c r="I304" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15193,12 +15193,12 @@
       </c>
       <c r="I305" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15241,12 +15241,12 @@
       </c>
       <c r="I306" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15289,12 +15289,12 @@
       </c>
       <c r="I307" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15337,12 +15337,12 @@
       </c>
       <c r="I308" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15385,12 +15385,12 @@
       </c>
       <c r="I309" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15433,12 +15433,12 @@
       </c>
       <c r="I310" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J310" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15481,12 +15481,12 @@
       </c>
       <c r="I311" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15529,12 +15529,12 @@
       </c>
       <c r="I312" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="I313" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15625,12 +15625,12 @@
       </c>
       <c r="I314" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15673,12 +15673,12 @@
       </c>
       <c r="I315" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J315" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="I316" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J316" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="I317" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15817,12 +15817,12 @@
       </c>
       <c r="I318" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I319" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J319" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15913,12 +15913,12 @@
       </c>
       <c r="I320" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -15961,12 +15961,12 @@
       </c>
       <c r="I321" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J321" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16009,12 +16009,12 @@
       </c>
       <c r="I322" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16057,12 +16057,12 @@
       </c>
       <c r="I323" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16105,12 +16105,12 @@
       </c>
       <c r="I324" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16153,12 +16153,12 @@
       </c>
       <c r="I325" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16201,12 +16201,12 @@
       </c>
       <c r="I326" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J326" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16249,12 +16249,12 @@
       </c>
       <c r="I327" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16297,12 +16297,12 @@
       </c>
       <c r="I328" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J328" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16345,12 +16345,12 @@
       </c>
       <c r="I329" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16393,12 +16393,12 @@
       </c>
       <c r="I330" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J330" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16441,12 +16441,12 @@
       </c>
       <c r="I331" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="I332" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J332" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16537,12 +16537,12 @@
       </c>
       <c r="I333" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16585,12 +16585,12 @@
       </c>
       <c r="I334" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J334" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16633,12 @@
       </c>
       <c r="I335" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16681,12 +16681,12 @@
       </c>
       <c r="I336" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J336" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16729,12 +16729,12 @@
       </c>
       <c r="I337" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16777,12 +16777,12 @@
       </c>
       <c r="I338" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16825,12 +16825,12 @@
       </c>
       <c r="I339" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="I340" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J340" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16921,12 +16921,12 @@
       </c>
       <c r="I341" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -16969,12 +16969,12 @@
       </c>
       <c r="I342" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17017,12 +17017,12 @@
       </c>
       <c r="I343" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17065,12 +17065,12 @@
       </c>
       <c r="I344" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J344" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17113,12 +17113,12 @@
       </c>
       <c r="I345" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J345" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17161,12 +17161,12 @@
       </c>
       <c r="I346" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17209,12 +17209,12 @@
       </c>
       <c r="I347" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17257,12 +17257,12 @@
       </c>
       <c r="I348" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17305,12 +17305,12 @@
       </c>
       <c r="I349" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17353,12 +17353,12 @@
       </c>
       <c r="I350" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="I351" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17449,12 +17449,12 @@
       </c>
       <c r="I352" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17497,12 +17497,12 @@
       </c>
       <c r="I353" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J353" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17545,12 +17545,12 @@
       </c>
       <c r="I354" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17593,12 +17593,12 @@
       </c>
       <c r="I355" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J355" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17641,12 +17641,12 @@
       </c>
       <c r="I356" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J356" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17689,12 +17689,12 @@
       </c>
       <c r="I357" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17737,12 +17737,12 @@
       </c>
       <c r="I358" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17785,12 +17785,12 @@
       </c>
       <c r="I359" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J359" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17833,12 +17833,12 @@
       </c>
       <c r="I360" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J360" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="I361" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J361" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17929,12 +17929,12 @@
       </c>
       <c r="I362" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J362" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -17977,12 +17977,12 @@
       </c>
       <c r="I363" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J363" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18025,12 +18025,12 @@
       </c>
       <c r="I364" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J364" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18073,12 +18073,12 @@
       </c>
       <c r="I365" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18121,12 +18121,12 @@
       </c>
       <c r="I366" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J366" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18169,12 +18169,12 @@
       </c>
       <c r="I367" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J367" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18217,12 +18217,12 @@
       </c>
       <c r="I368" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J368" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18265,12 +18265,12 @@
       </c>
       <c r="I369" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J369" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18313,12 +18313,12 @@
       </c>
       <c r="I370" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J370" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18361,12 +18361,12 @@
       </c>
       <c r="I371" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J371" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18409,12 +18409,12 @@
       </c>
       <c r="I372" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J372" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18457,12 +18457,12 @@
       </c>
       <c r="I373" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J373" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
@@ -18505,19 +18505,19 @@
       </c>
       <c r="I374" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J374" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="8" t="inlineStr">
         <is>
-          <t>MO88810AB000</t>
+          <t>SBL7-2001KM</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11753</t>
+          <t>WAMAS01-11757</t>
         </is>
       </c>
       <c r="E375" s="9" t="n">
@@ -18548,24 +18548,24 @@
       </c>
       <c r="H375" s="9" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>BL7m</t>
         </is>
       </c>
       <c r="I375" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="8" t="inlineStr">
         <is>
-          <t>MO88810BV000</t>
+          <t>SSW3-0008</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11754</t>
+          <t>WAMAS01-11758</t>
         </is>
       </c>
       <c r="E376" s="9" t="n">
@@ -18596,24 +18596,24 @@
       </c>
       <c r="H376" s="9" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="I376" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J376" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="8" t="inlineStr">
         <is>
-          <t>MO88820AB000</t>
+          <t>SSW3-0008KV</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11755</t>
+          <t>WAMAS01-11759</t>
         </is>
       </c>
       <c r="E377" s="9" t="n">
@@ -18644,24 +18644,24 @@
       </c>
       <c r="H377" s="9" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="I377" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="8" t="inlineStr">
         <is>
-          <t>MO88820I7000</t>
+          <t>SSW3-0014</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11756</t>
+          <t>WAMAS01-11760</t>
         </is>
       </c>
       <c r="E378" s="9" t="n">
@@ -18692,24 +18692,24 @@
       </c>
       <c r="H378" s="9" t="inlineStr">
         <is>
-          <t>SUD</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="I378" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J378" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="8" t="inlineStr">
         <is>
-          <t>SBL7-2001KM</t>
+          <t>SSW3-0022</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11757</t>
+          <t>WAMAS01-11761</t>
         </is>
       </c>
       <c r="E379" s="9" t="n">
@@ -18740,24 +18740,24 @@
       </c>
       <c r="H379" s="9" t="inlineStr">
         <is>
-          <t>BL7m</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I379" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J379" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="8" t="inlineStr">
         <is>
-          <t>SSW3-0008</t>
+          <t>SSW3-0022KM</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11758</t>
+          <t>WAMAS01-11762</t>
         </is>
       </c>
       <c r="E380" s="9" t="n">
@@ -18788,24 +18788,24 @@
       </c>
       <c r="H380" s="9" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I380" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J380" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="8" t="inlineStr">
         <is>
-          <t>SSW3-0008KV</t>
+          <t>SSW3-0022KV</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11759</t>
+          <t>WAMAS01-11763</t>
         </is>
       </c>
       <c r="E381" s="9" t="n">
@@ -18836,24 +18836,24 @@
       </c>
       <c r="H381" s="9" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I381" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J381" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="8" t="inlineStr">
         <is>
-          <t>SSW3-0014</t>
+          <t>SSW3-0023</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11760</t>
+          <t>WAMAS01-11764</t>
         </is>
       </c>
       <c r="E382" s="9" t="n">
@@ -18884,24 +18884,24 @@
       </c>
       <c r="H382" s="9" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>EA1C</t>
         </is>
       </c>
       <c r="I382" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J382" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="8" t="inlineStr">
         <is>
-          <t>SSW3-0022</t>
+          <t>X89880GJ000NNB</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>WAMAS01-11761</t>
+          <t>WAMAS01-11765</t>
         </is>
       </c>
       <c r="E383" s="9" t="n">
@@ -18932,209 +18932,17 @@
       </c>
       <c r="H383" s="9" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>BJ1</t>
         </is>
       </c>
       <c r="I383" s="8" t="inlineStr">
         <is>
-          <t>기준정보 누락</t>
+          <t>라인코드 누락</t>
         </is>
       </c>
       <c r="J383" s="12" t="inlineStr">
         <is>
-          <t>기준정보 등록필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="8" t="inlineStr">
-        <is>
-          <t>SSW3-0022KM</t>
-        </is>
-      </c>
-      <c r="B384" s="9" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
-      </c>
-      <c r="C384" s="9" t="inlineStr">
-        <is>
-          <t>WAMAS01</t>
-        </is>
-      </c>
-      <c r="D384" s="8" t="inlineStr">
-        <is>
-          <t>WAMAS01-11762</t>
-        </is>
-      </c>
-      <c r="E384" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F384" s="9" t="inlineStr">
-        <is>
-          <t>정단가</t>
-        </is>
-      </c>
-      <c r="G384" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H384" s="9" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="I384" s="8" t="inlineStr">
-        <is>
-          <t>기준정보 누락</t>
-        </is>
-      </c>
-      <c r="J384" s="12" t="inlineStr">
-        <is>
-          <t>기준정보 등록필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="8" t="inlineStr">
-        <is>
-          <t>SSW3-0022KV</t>
-        </is>
-      </c>
-      <c r="B385" s="9" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
-      </c>
-      <c r="C385" s="9" t="inlineStr">
-        <is>
-          <t>WAMAS01</t>
-        </is>
-      </c>
-      <c r="D385" s="8" t="inlineStr">
-        <is>
-          <t>WAMAS01-11763</t>
-        </is>
-      </c>
-      <c r="E385" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F385" s="9" t="inlineStr">
-        <is>
-          <t>정단가</t>
-        </is>
-      </c>
-      <c r="G385" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H385" s="9" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="I385" s="8" t="inlineStr">
-        <is>
-          <t>기준정보 누락</t>
-        </is>
-      </c>
-      <c r="J385" s="12" t="inlineStr">
-        <is>
-          <t>기준정보 등록필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="8" t="inlineStr">
-        <is>
-          <t>SSW3-0023</t>
-        </is>
-      </c>
-      <c r="B386" s="9" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
-      </c>
-      <c r="C386" s="9" t="inlineStr">
-        <is>
-          <t>WAMAS01</t>
-        </is>
-      </c>
-      <c r="D386" s="8" t="inlineStr">
-        <is>
-          <t>WAMAS01-11764</t>
-        </is>
-      </c>
-      <c r="E386" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F386" s="9" t="inlineStr">
-        <is>
-          <t>정단가</t>
-        </is>
-      </c>
-      <c r="G386" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H386" s="9" t="inlineStr">
-        <is>
-          <t>EA1C</t>
-        </is>
-      </c>
-      <c r="I386" s="8" t="inlineStr">
-        <is>
-          <t>기준정보 누락</t>
-        </is>
-      </c>
-      <c r="J386" s="12" t="inlineStr">
-        <is>
-          <t>기준정보 등록필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="8" t="inlineStr">
-        <is>
-          <t>X89880GJ000NNB</t>
-        </is>
-      </c>
-      <c r="B387" s="9" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
-      </c>
-      <c r="C387" s="9" t="inlineStr">
-        <is>
-          <t>WAMAS01</t>
-        </is>
-      </c>
-      <c r="D387" s="8" t="inlineStr">
-        <is>
-          <t>WAMAS01-11765</t>
-        </is>
-      </c>
-      <c r="E387" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F387" s="9" t="inlineStr">
-        <is>
-          <t>정단가</t>
-        </is>
-      </c>
-      <c r="G387" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H387" s="9" t="inlineStr">
-        <is>
-          <t>BJ1</t>
-        </is>
-      </c>
-      <c r="I387" s="8" t="inlineStr">
-        <is>
-          <t>기준정보 누락</t>
-        </is>
-      </c>
-      <c r="J387" s="12" t="inlineStr">
-        <is>
-          <t>기준정보 등록필요</t>
+          <t>라인코드 등록필요</t>
         </is>
       </c>
     </row>
